--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_02_2024.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_02_2024.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\báo cáo 1\KHNV2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\update TTBC\2024_T8_05_KHNV 5 năm\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -387,13 +387,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -491,9 +500,36 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -509,32 +545,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -847,20 +862,20 @@
     <row r="1" spans="1:21">
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="4"/>
@@ -873,21 +888,21 @@
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="4"/>
@@ -898,221 +913,221 @@
       <c r="F3" s="28"/>
       <c r="G3" s="28"/>
       <c r="H3" s="28"/>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
     </row>
     <row r="4" spans="1:21">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="21.95" customHeight="1">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
       <c r="T5" s="5"/>
     </row>
     <row r="6" spans="1:21" ht="23.25" customHeight="1">
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
     </row>
     <row r="7" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35" t="s">
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35" t="s">
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
       <c r="Q7" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="43"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="42"/>
     </row>
     <row r="8" spans="1:21" ht="32.25" customHeight="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="44" t="s">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44" t="s">
+      <c r="G8" s="42"/>
+      <c r="H8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="44" t="s">
+      <c r="J8" s="42"/>
+      <c r="K8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="L8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="44" t="s">
+      <c r="M8" s="42"/>
+      <c r="N8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="O8" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="44" t="s">
+      <c r="P8" s="42"/>
+      <c r="Q8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="R8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S8" s="43"/>
+      <c r="S8" s="42"/>
       <c r="T8" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="43"/>
+      <c r="U8" s="42"/>
     </row>
     <row r="9" spans="1:21" ht="17.25" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="47" t="s">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="45"/>
-      <c r="I9" s="47" t="s">
+      <c r="H9" s="39"/>
+      <c r="I9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="47" t="s">
+      <c r="J9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="47" t="s">
+      <c r="K9" s="39"/>
+      <c r="L9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="47" t="s">
+      <c r="M9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="45"/>
-      <c r="O9" s="47" t="s">
+      <c r="N9" s="39"/>
+      <c r="O9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="47" t="s">
+      <c r="P9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="47" t="s">
+      <c r="Q9" s="39"/>
+      <c r="R9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="47" t="s">
+      <c r="S9" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="T9" s="47" t="s">
+      <c r="T9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="U9" s="47" t="s">
+      <c r="U9" s="35" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="12.75">
-      <c r="A10" s="35"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1">
       <c r="A11" s="6">
@@ -2905,71 +2920,94 @@
       <c r="T86" s="26"/>
       <c r="U86" s="26"/>
     </row>
+    <row r="87" spans="1:21">
+      <c r="A87" s="50"/>
+      <c r="B87" s="50"/>
+      <c r="C87" s="50"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="51"/>
+      <c r="K87" s="51"/>
+      <c r="L87" s="51"/>
+      <c r="M87" s="51"/>
+      <c r="N87" s="51"/>
+      <c r="O87" s="51"/>
+      <c r="P87" s="51"/>
+      <c r="Q87" s="51"/>
+      <c r="R87" s="51"/>
+      <c r="S87" s="51"/>
+      <c r="T87" s="51"/>
+      <c r="U87" s="51"/>
+    </row>
     <row r="88" spans="1:21">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
-      <c r="I88" s="48" t="s">
+      <c r="I88" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="J88" s="48"/>
-      <c r="K88" s="48"/>
-      <c r="L88" s="48"/>
-      <c r="M88" s="48"/>
-      <c r="N88" s="48"/>
-      <c r="O88" s="48"/>
-      <c r="P88" s="48"/>
-      <c r="Q88" s="48"/>
-      <c r="R88" s="48"/>
-      <c r="S88" s="48"/>
-      <c r="T88" s="48"/>
-      <c r="U88" s="48"/>
+      <c r="J88" s="36"/>
+      <c r="K88" s="36"/>
+      <c r="L88" s="36"/>
+      <c r="M88" s="36"/>
+      <c r="N88" s="36"/>
+      <c r="O88" s="36"/>
+      <c r="P88" s="36"/>
+      <c r="Q88" s="36"/>
+      <c r="R88" s="36"/>
+      <c r="S88" s="36"/>
+      <c r="T88" s="36"/>
+      <c r="U88" s="36"/>
     </row>
     <row r="89" spans="1:21" ht="21" customHeight="1">
       <c r="A89" s="11"/>
-      <c r="B89" s="49" t="s">
+      <c r="B89" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="49"/>
-      <c r="H89" s="49" t="s">
+      <c r="C89" s="37"/>
+      <c r="H89" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="I89" s="49"/>
-      <c r="J89" s="49"/>
-      <c r="K89" s="49"/>
-      <c r="L89" s="49"/>
-      <c r="M89" s="49"/>
-      <c r="N89" s="49"/>
-      <c r="O89" s="49"/>
-      <c r="P89" s="49"/>
-      <c r="Q89" s="49"/>
-      <c r="R89" s="49"/>
-      <c r="S89" s="49"/>
-      <c r="T89" s="49"/>
-      <c r="U89" s="49"/>
+      <c r="I89" s="37"/>
+      <c r="J89" s="37"/>
+      <c r="K89" s="37"/>
+      <c r="L89" s="37"/>
+      <c r="M89" s="37"/>
+      <c r="N89" s="37"/>
+      <c r="O89" s="37"/>
+      <c r="P89" s="37"/>
+      <c r="Q89" s="37"/>
+      <c r="R89" s="37"/>
+      <c r="S89" s="37"/>
+      <c r="T89" s="37"/>
+      <c r="U89" s="37"/>
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="12"/>
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="48"/>
-      <c r="H90" s="48" t="s">
+      <c r="C90" s="36"/>
+      <c r="H90" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48"/>
-      <c r="L90" s="48"/>
-      <c r="M90" s="48"/>
-      <c r="N90" s="48"/>
-      <c r="O90" s="48"/>
-      <c r="P90" s="48"/>
-      <c r="Q90" s="48"/>
-      <c r="R90" s="48"/>
-      <c r="S90" s="48"/>
-      <c r="T90" s="48"/>
-      <c r="U90" s="48"/>
+      <c r="I90" s="36"/>
+      <c r="J90" s="36"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="36"/>
+      <c r="M90" s="36"/>
+      <c r="N90" s="36"/>
+      <c r="O90" s="36"/>
+      <c r="P90" s="36"/>
+      <c r="Q90" s="36"/>
+      <c r="R90" s="36"/>
+      <c r="S90" s="36"/>
+      <c r="T90" s="36"/>
+      <c r="U90" s="36"/>
     </row>
     <row r="91" spans="1:21" ht="18" customHeight="1">
       <c r="A91" s="2"/>
@@ -2981,6 +3019,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="J1:U1"/>
+    <mergeCell ref="A5:S5"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="I2:U2"/>
+    <mergeCell ref="I3:U3"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="L9:L10"/>
     <mergeCell ref="U9:U10"/>
     <mergeCell ref="I88:U88"/>
     <mergeCell ref="B89:C89"/>
@@ -2997,32 +3061,6 @@
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="Q8:Q10"/>
     <mergeCell ref="R8:S8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:U7"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="J1:U1"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="I2:U2"/>
-    <mergeCell ref="I3:U3"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="E7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="33" orientation="portrait" r:id="rId1"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_02_2024.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_02_2024.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\update TTBC\2024_T8_05_KHNV 5 năm\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\báo cáo 1\KHNV2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>Biểu số: 02/NHCS-KH</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>NGÂN HÀNG CHÍNH SÁCH XÃ HỘI</t>
+  </si>
+  <si>
+    <t>MÃ CHỈ TIÊU</t>
   </si>
 </sst>
 </file>
@@ -236,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -387,22 +390,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -500,6 +494,42 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -508,48 +538,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -833,303 +821,313 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="64.5703125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7" style="2" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.5703125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="H1" s="3"/>
+    <row r="1" spans="1:22">
       <c r="I1" s="3"/>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="3"/>
+      <c r="K1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="4"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="27"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="27"/>
+      <c r="J2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="4"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="28"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
       <c r="G3" s="28"/>
       <c r="H3" s="28"/>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="28"/>
+      <c r="J3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="B4" s="4"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:21" ht="21.95" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:22" ht="21.95" customHeight="1">
+      <c r="A5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:21" ht="23.25" customHeight="1">
-      <c r="J6" s="47" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="5"/>
+    </row>
+    <row r="6" spans="1:22" ht="23.25" customHeight="1">
+      <c r="K6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-    </row>
-    <row r="7" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A7" s="43" t="s">
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+    </row>
+    <row r="7" spans="1:22" ht="33.75" customHeight="1">
+      <c r="A7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="D7" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="E7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="F7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43" t="s">
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43" t="s">
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43" t="s">
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="41" t="s">
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="42"/>
-    </row>
-    <row r="8" spans="1:21" ht="32.25" customHeight="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="38" t="s">
+      <c r="S7" s="45"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="46"/>
+    </row>
+    <row r="8" spans="1:22" ht="32.25" customHeight="1">
+      <c r="A8" s="35"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="G8" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="46"/>
+      <c r="I8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="J8" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="46"/>
+      <c r="L8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="M8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="42"/>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="46"/>
+      <c r="O8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="41" t="s">
+      <c r="P8" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="38" t="s">
+      <c r="Q8" s="46"/>
+      <c r="R8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="R8" s="41" t="s">
+      <c r="S8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="S8" s="42"/>
-      <c r="T8" s="41" t="s">
+      <c r="T8" s="46"/>
+      <c r="U8" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="42"/>
-    </row>
-    <row r="9" spans="1:21" ht="17.25" customHeight="1">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="35" t="s">
+      <c r="V8" s="46"/>
+    </row>
+    <row r="9" spans="1:22" ht="17.25" customHeight="1">
+      <c r="A9" s="35"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="H9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="37"/>
+      <c r="J9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="K9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="35" t="s">
+      <c r="L9" s="37"/>
+      <c r="M9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="35" t="s">
+      <c r="N9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="39"/>
-      <c r="O9" s="35" t="s">
+      <c r="O9" s="37"/>
+      <c r="P9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="35" t="s">
+      <c r="Q9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="35" t="s">
+      <c r="R9" s="37"/>
+      <c r="S9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="35" t="s">
+      <c r="T9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="T9" s="35" t="s">
+      <c r="U9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="U9" s="35" t="s">
+      <c r="V9" s="47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="12.75">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-    </row>
-    <row r="11" spans="1:21" ht="15" customHeight="1">
+    <row r="10" spans="1:22" ht="27.75" customHeight="1">
+      <c r="A10" s="35"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+    </row>
+    <row r="11" spans="1:22" ht="15" customHeight="1">
       <c r="A11" s="6">
         <v>1</v>
       </c>
@@ -1193,17 +1191,20 @@
       <c r="U11" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="V11" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
@@ -1211,17 +1212,18 @@
       <c r="N12" s="21"/>
       <c r="O12" s="21"/>
       <c r="P12" s="21"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="22"/>
       <c r="S12" s="21"/>
       <c r="T12" s="21"/>
       <c r="U12" s="21"/>
-    </row>
-    <row r="13" spans="1:21" s="1" customFormat="1">
+      <c r="V12" s="21"/>
+    </row>
+    <row r="13" spans="1:22" s="1" customFormat="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="17"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
@@ -1239,12 +1241,13 @@
       <c r="S13" s="17"/>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
-    </row>
-    <row r="14" spans="1:21" s="1" customFormat="1">
+      <c r="V13" s="17"/>
+    </row>
+    <row r="14" spans="1:22" s="1" customFormat="1">
       <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="17"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
@@ -1262,12 +1265,13 @@
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
-    </row>
-    <row r="15" spans="1:21" s="7" customFormat="1">
+      <c r="V14" s="17"/>
+    </row>
+    <row r="15" spans="1:22" s="7" customFormat="1">
       <c r="A15" s="31"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
@@ -1285,12 +1289,13 @@
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
-    </row>
-    <row r="16" spans="1:21" s="7" customFormat="1">
+      <c r="V15" s="17"/>
+    </row>
+    <row r="16" spans="1:22" s="7" customFormat="1">
       <c r="A16" s="31"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
@@ -1308,12 +1313,13 @@
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
-    </row>
-    <row r="17" spans="1:21" s="8" customFormat="1">
+      <c r="V16" s="17"/>
+    </row>
+    <row r="17" spans="1:22" s="8" customFormat="1">
       <c r="A17" s="31"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -1331,12 +1337,13 @@
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
-    </row>
-    <row r="18" spans="1:21" s="8" customFormat="1">
+      <c r="V17" s="17"/>
+    </row>
+    <row r="18" spans="1:22" s="8" customFormat="1">
       <c r="A18" s="31"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="17"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
@@ -1354,12 +1361,13 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
-    </row>
-    <row r="19" spans="1:21" s="8" customFormat="1">
+      <c r="V18" s="17"/>
+    </row>
+    <row r="19" spans="1:22" s="8" customFormat="1">
       <c r="A19" s="31"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="17"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
@@ -1377,11 +1385,12 @@
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="17"/>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="31"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="17"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
@@ -1400,11 +1409,12 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="17"/>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="31"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="17"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
@@ -1423,12 +1433,13 @@
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="17"/>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="31"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="18"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
@@ -1446,12 +1457,13 @@
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
       <c r="U22" s="17"/>
-    </row>
-    <row r="23" spans="1:21" s="1" customFormat="1">
+      <c r="V22" s="17"/>
+    </row>
+    <row r="23" spans="1:22" s="1" customFormat="1">
       <c r="A23" s="31"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="17"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="18"/>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
@@ -1469,12 +1481,13 @@
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
-    </row>
-    <row r="24" spans="1:21" s="7" customFormat="1">
+      <c r="V23" s="17"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1">
       <c r="A24" s="31"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="29"/>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="30"/>
@@ -1492,12 +1505,13 @@
       <c r="S24" s="30"/>
       <c r="T24" s="30"/>
       <c r="U24" s="30"/>
-    </row>
-    <row r="25" spans="1:21">
+      <c r="V24" s="30"/>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="31"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="17"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="18"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
@@ -1515,12 +1529,13 @@
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
-    </row>
-    <row r="26" spans="1:21">
+      <c r="V25" s="17"/>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="31"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="17"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="18"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
@@ -1538,12 +1553,13 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
       <c r="U26" s="17"/>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="17"/>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="31"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="17"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="18"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
@@ -1561,12 +1577,13 @@
       <c r="S27" s="17"/>
       <c r="T27" s="17"/>
       <c r="U27" s="17"/>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="17"/>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="31"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="17"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="18"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
@@ -1584,12 +1601,13 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="17"/>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="31"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="17"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="18"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
@@ -1607,12 +1625,13 @@
       <c r="S29" s="17"/>
       <c r="T29" s="17"/>
       <c r="U29" s="17"/>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="17"/>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="18"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
@@ -1630,12 +1649,13 @@
       <c r="S30" s="17"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="V30" s="17"/>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="31"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="17"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="18"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
@@ -1653,12 +1673,13 @@
       <c r="S31" s="17"/>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31" s="17"/>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="31"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="17"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="18"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
@@ -1676,12 +1697,13 @@
       <c r="S32" s="17"/>
       <c r="T32" s="17"/>
       <c r="U32" s="17"/>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="V32" s="17"/>
+    </row>
+    <row r="33" spans="1:23">
       <c r="A33" s="31"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="18"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="17"/>
@@ -1699,12 +1721,13 @@
       <c r="S33" s="17"/>
       <c r="T33" s="17"/>
       <c r="U33" s="17"/>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="V33" s="17"/>
+    </row>
+    <row r="34" spans="1:23">
       <c r="A34" s="31"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="18"/>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
@@ -1722,12 +1745,13 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
       <c r="U34" s="17"/>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="V34" s="17"/>
+    </row>
+    <row r="35" spans="1:23">
       <c r="A35" s="31"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="17"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="18"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
@@ -1745,12 +1769,13 @@
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
       <c r="U35" s="17"/>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="V35" s="17"/>
+    </row>
+    <row r="36" spans="1:23">
       <c r="A36" s="31"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="17"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="18"/>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
@@ -1768,12 +1793,13 @@
       <c r="S36" s="17"/>
       <c r="T36" s="17"/>
       <c r="U36" s="17"/>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="V36" s="17"/>
+    </row>
+    <row r="37" spans="1:23">
       <c r="A37" s="31"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="17"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="18"/>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
@@ -1791,12 +1817,13 @@
       <c r="S37" s="17"/>
       <c r="T37" s="17"/>
       <c r="U37" s="17"/>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="V37" s="17"/>
+    </row>
+    <row r="38" spans="1:23">
       <c r="A38" s="31"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="17"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="18"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
@@ -1814,12 +1841,13 @@
       <c r="S38" s="17"/>
       <c r="T38" s="17"/>
       <c r="U38" s="17"/>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="V38" s="17"/>
+    </row>
+    <row r="39" spans="1:23">
       <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="17"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="18"/>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
@@ -1837,12 +1865,13 @@
       <c r="S39" s="17"/>
       <c r="T39" s="17"/>
       <c r="U39" s="17"/>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="V39" s="17"/>
+    </row>
+    <row r="40" spans="1:23">
       <c r="A40" s="31"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="17"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="18"/>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
@@ -1860,12 +1889,13 @@
       <c r="S40" s="17"/>
       <c r="T40" s="17"/>
       <c r="U40" s="17"/>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="V40" s="17"/>
+    </row>
+    <row r="41" spans="1:23">
       <c r="A41" s="31"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="17"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="18"/>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
@@ -1883,12 +1913,13 @@
       <c r="S41" s="17"/>
       <c r="T41" s="17"/>
       <c r="U41" s="17"/>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="V41" s="17"/>
+    </row>
+    <row r="42" spans="1:23">
       <c r="A42" s="31"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="17"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="18"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
@@ -1906,12 +1937,13 @@
       <c r="S42" s="17"/>
       <c r="T42" s="17"/>
       <c r="U42" s="17"/>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="V42" s="17"/>
+    </row>
+    <row r="43" spans="1:23">
       <c r="A43" s="31"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="17"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="17"/>
@@ -1929,12 +1961,13 @@
       <c r="S43" s="17"/>
       <c r="T43" s="17"/>
       <c r="U43" s="17"/>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="V43" s="17"/>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44" s="31"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="17"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="19"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
       <c r="G44" s="17"/>
@@ -1952,12 +1985,13 @@
       <c r="S44" s="17"/>
       <c r="T44" s="17"/>
       <c r="U44" s="17"/>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1">
+      <c r="V44" s="17"/>
+    </row>
+    <row r="45" spans="1:23" s="7" customFormat="1">
       <c r="A45" s="31"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="17"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="19"/>
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
@@ -1975,13 +2009,14 @@
       <c r="S45" s="17"/>
       <c r="T45" s="17"/>
       <c r="U45" s="17"/>
-      <c r="V45" s="2"/>
-    </row>
-    <row r="46" spans="1:22">
+      <c r="V45" s="17"/>
+      <c r="W45" s="2"/>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46" s="31"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="17"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="19"/>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
@@ -1999,12 +2034,13 @@
       <c r="S46" s="17"/>
       <c r="T46" s="17"/>
       <c r="U46" s="17"/>
-    </row>
-    <row r="47" spans="1:22">
+      <c r="V46" s="17"/>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="17"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="18"/>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
@@ -2022,12 +2058,13 @@
       <c r="S47" s="17"/>
       <c r="T47" s="17"/>
       <c r="U47" s="17"/>
-    </row>
-    <row r="48" spans="1:22">
+      <c r="V47" s="17"/>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48" s="31"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="17"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="18"/>
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
       <c r="G48" s="17"/>
@@ -2045,12 +2082,13 @@
       <c r="S48" s="17"/>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="17"/>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="31"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="17"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="18"/>
       <c r="E49" s="17"/>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
@@ -2068,12 +2106,13 @@
       <c r="S49" s="17"/>
       <c r="T49" s="17"/>
       <c r="U49" s="17"/>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="17"/>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" s="31"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="17"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="18"/>
       <c r="E50" s="17"/>
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
@@ -2091,12 +2130,13 @@
       <c r="S50" s="17"/>
       <c r="T50" s="17"/>
       <c r="U50" s="17"/>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="17"/>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="31"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="17"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="18"/>
       <c r="E51" s="17"/>
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
@@ -2114,12 +2154,13 @@
       <c r="S51" s="17"/>
       <c r="T51" s="17"/>
       <c r="U51" s="17"/>
-    </row>
-    <row r="52" spans="1:21" s="9" customFormat="1">
+      <c r="V51" s="17"/>
+    </row>
+    <row r="52" spans="1:22" s="9" customFormat="1">
       <c r="A52" s="31"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="17"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="18"/>
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
@@ -2137,12 +2178,13 @@
       <c r="S52" s="17"/>
       <c r="T52" s="17"/>
       <c r="U52" s="17"/>
-    </row>
-    <row r="53" spans="1:21" s="9" customFormat="1">
+      <c r="V52" s="17"/>
+    </row>
+    <row r="53" spans="1:22" s="9" customFormat="1">
       <c r="A53" s="31"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="17"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="18"/>
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
@@ -2160,12 +2202,13 @@
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
       <c r="U53" s="17"/>
-    </row>
-    <row r="54" spans="1:21" s="9" customFormat="1">
+      <c r="V53" s="17"/>
+    </row>
+    <row r="54" spans="1:22" s="9" customFormat="1">
       <c r="A54" s="31"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="17"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="18"/>
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
@@ -2183,12 +2226,13 @@
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
       <c r="U54" s="17"/>
-    </row>
-    <row r="55" spans="1:21" s="9" customFormat="1">
+      <c r="V54" s="17"/>
+    </row>
+    <row r="55" spans="1:22" s="9" customFormat="1">
       <c r="A55" s="31"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="17"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="18"/>
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
@@ -2206,12 +2250,13 @@
       <c r="S55" s="17"/>
       <c r="T55" s="17"/>
       <c r="U55" s="17"/>
-    </row>
-    <row r="56" spans="1:21" s="9" customFormat="1">
+      <c r="V55" s="17"/>
+    </row>
+    <row r="56" spans="1:22" s="9" customFormat="1">
       <c r="A56" s="31"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="17"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="18"/>
       <c r="E56" s="17"/>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
@@ -2229,12 +2274,13 @@
       <c r="S56" s="17"/>
       <c r="T56" s="17"/>
       <c r="U56" s="17"/>
-    </row>
-    <row r="57" spans="1:21" s="9" customFormat="1">
+      <c r="V56" s="17"/>
+    </row>
+    <row r="57" spans="1:22" s="9" customFormat="1">
       <c r="A57" s="31"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="17"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="18"/>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
@@ -2252,12 +2298,13 @@
       <c r="S57" s="17"/>
       <c r="T57" s="17"/>
       <c r="U57" s="17"/>
-    </row>
-    <row r="58" spans="1:21" s="7" customFormat="1">
+      <c r="V57" s="17"/>
+    </row>
+    <row r="58" spans="1:22" s="7" customFormat="1">
       <c r="A58" s="31"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="17"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="18"/>
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
@@ -2275,12 +2322,13 @@
       <c r="S58" s="17"/>
       <c r="T58" s="17"/>
       <c r="U58" s="17"/>
-    </row>
-    <row r="59" spans="1:21" s="7" customFormat="1">
+      <c r="V58" s="17"/>
+    </row>
+    <row r="59" spans="1:22" s="7" customFormat="1">
       <c r="A59" s="31"/>
-      <c r="B59" s="32"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="17"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="18"/>
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
@@ -2298,12 +2346,13 @@
       <c r="S59" s="17"/>
       <c r="T59" s="17"/>
       <c r="U59" s="17"/>
-    </row>
-    <row r="60" spans="1:21" s="7" customFormat="1">
+      <c r="V59" s="17"/>
+    </row>
+    <row r="60" spans="1:22" s="7" customFormat="1">
       <c r="A60" s="31"/>
-      <c r="B60" s="32"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="17"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="18"/>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
@@ -2321,12 +2370,13 @@
       <c r="S60" s="17"/>
       <c r="T60" s="17"/>
       <c r="U60" s="17"/>
-    </row>
-    <row r="61" spans="1:21" s="7" customFormat="1">
+      <c r="V60" s="17"/>
+    </row>
+    <row r="61" spans="1:22" s="7" customFormat="1">
       <c r="A61" s="31"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="17"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="18"/>
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
@@ -2344,12 +2394,13 @@
       <c r="S61" s="17"/>
       <c r="T61" s="17"/>
       <c r="U61" s="17"/>
-    </row>
-    <row r="62" spans="1:21" s="7" customFormat="1">
+      <c r="V61" s="17"/>
+    </row>
+    <row r="62" spans="1:22" s="7" customFormat="1">
       <c r="A62" s="31"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="17"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="19"/>
       <c r="E62" s="17"/>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
@@ -2367,12 +2418,13 @@
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
       <c r="U62" s="17"/>
-    </row>
-    <row r="63" spans="1:21" s="7" customFormat="1">
+      <c r="V62" s="17"/>
+    </row>
+    <row r="63" spans="1:22" s="7" customFormat="1">
       <c r="A63" s="31"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="17"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="19"/>
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
       <c r="G63" s="17"/>
@@ -2390,12 +2442,13 @@
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
       <c r="U63" s="17"/>
-    </row>
-    <row r="64" spans="1:21" s="7" customFormat="1">
+      <c r="V63" s="17"/>
+    </row>
+    <row r="64" spans="1:22" s="7" customFormat="1">
       <c r="A64" s="31"/>
-      <c r="B64" s="32"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="17"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="19"/>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
@@ -2413,12 +2466,13 @@
       <c r="S64" s="17"/>
       <c r="T64" s="17"/>
       <c r="U64" s="17"/>
-    </row>
-    <row r="65" spans="1:21" s="7" customFormat="1">
+      <c r="V64" s="17"/>
+    </row>
+    <row r="65" spans="1:22" s="7" customFormat="1">
       <c r="A65" s="31"/>
-      <c r="B65" s="32"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="17"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="18"/>
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17"/>
@@ -2436,12 +2490,13 @@
       <c r="S65" s="17"/>
       <c r="T65" s="17"/>
       <c r="U65" s="17"/>
-    </row>
-    <row r="66" spans="1:21" s="7" customFormat="1">
+      <c r="V65" s="17"/>
+    </row>
+    <row r="66" spans="1:22" s="7" customFormat="1">
       <c r="A66" s="31"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="17"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="18"/>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
@@ -2459,12 +2514,13 @@
       <c r="S66" s="17"/>
       <c r="T66" s="17"/>
       <c r="U66" s="17"/>
-    </row>
-    <row r="67" spans="1:21" s="7" customFormat="1">
+      <c r="V66" s="17"/>
+    </row>
+    <row r="67" spans="1:22" s="7" customFormat="1">
       <c r="A67" s="31"/>
-      <c r="B67" s="32"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="17"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="18"/>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
@@ -2482,12 +2538,13 @@
       <c r="S67" s="17"/>
       <c r="T67" s="17"/>
       <c r="U67" s="17"/>
-    </row>
-    <row r="68" spans="1:21" s="7" customFormat="1">
+      <c r="V67" s="17"/>
+    </row>
+    <row r="68" spans="1:22" s="7" customFormat="1">
       <c r="A68" s="31"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="17"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="18"/>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
@@ -2505,12 +2562,13 @@
       <c r="S68" s="17"/>
       <c r="T68" s="17"/>
       <c r="U68" s="17"/>
-    </row>
-    <row r="69" spans="1:21" s="7" customFormat="1">
+      <c r="V68" s="17"/>
+    </row>
+    <row r="69" spans="1:22" s="7" customFormat="1">
       <c r="A69" s="31"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="17"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="18"/>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
@@ -2528,12 +2586,13 @@
       <c r="S69" s="17"/>
       <c r="T69" s="17"/>
       <c r="U69" s="17"/>
-    </row>
-    <row r="70" spans="1:21" s="7" customFormat="1">
+      <c r="V69" s="17"/>
+    </row>
+    <row r="70" spans="1:22" s="7" customFormat="1">
       <c r="A70" s="31"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="17"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="18"/>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
@@ -2551,12 +2610,13 @@
       <c r="S70" s="17"/>
       <c r="T70" s="17"/>
       <c r="U70" s="17"/>
-    </row>
-    <row r="71" spans="1:21" s="7" customFormat="1">
+      <c r="V70" s="17"/>
+    </row>
+    <row r="71" spans="1:22" s="7" customFormat="1">
       <c r="A71" s="31"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="17"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="18"/>
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
@@ -2574,12 +2634,13 @@
       <c r="S71" s="17"/>
       <c r="T71" s="17"/>
       <c r="U71" s="17"/>
-    </row>
-    <row r="72" spans="1:21" s="7" customFormat="1">
+      <c r="V71" s="17"/>
+    </row>
+    <row r="72" spans="1:22" s="7" customFormat="1">
       <c r="A72" s="31"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="17"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="18"/>
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
@@ -2597,12 +2658,13 @@
       <c r="S72" s="17"/>
       <c r="T72" s="17"/>
       <c r="U72" s="17"/>
-    </row>
-    <row r="73" spans="1:21" s="7" customFormat="1">
+      <c r="V72" s="17"/>
+    </row>
+    <row r="73" spans="1:22" s="7" customFormat="1">
       <c r="A73" s="31"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="17"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="18"/>
       <c r="E73" s="17"/>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
@@ -2620,12 +2682,13 @@
       <c r="S73" s="17"/>
       <c r="T73" s="17"/>
       <c r="U73" s="17"/>
-    </row>
-    <row r="74" spans="1:21" s="7" customFormat="1">
+      <c r="V73" s="17"/>
+    </row>
+    <row r="74" spans="1:22" s="7" customFormat="1">
       <c r="A74" s="31"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="17"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="18"/>
       <c r="E74" s="17"/>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
@@ -2643,12 +2706,13 @@
       <c r="S74" s="17"/>
       <c r="T74" s="17"/>
       <c r="U74" s="17"/>
-    </row>
-    <row r="75" spans="1:21" s="7" customFormat="1">
+      <c r="V74" s="17"/>
+    </row>
+    <row r="75" spans="1:22" s="7" customFormat="1">
       <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="17"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="18"/>
       <c r="E75" s="17"/>
       <c r="F75" s="17"/>
       <c r="G75" s="17"/>
@@ -2666,12 +2730,13 @@
       <c r="S75" s="17"/>
       <c r="T75" s="17"/>
       <c r="U75" s="17"/>
-    </row>
-    <row r="76" spans="1:21">
+      <c r="V75" s="17"/>
+    </row>
+    <row r="76" spans="1:22">
       <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="17"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="18"/>
       <c r="E76" s="17"/>
       <c r="F76" s="17"/>
       <c r="G76" s="17"/>
@@ -2689,12 +2754,13 @@
       <c r="S76" s="17"/>
       <c r="T76" s="17"/>
       <c r="U76" s="17"/>
-    </row>
-    <row r="77" spans="1:21">
+      <c r="V76" s="17"/>
+    </row>
+    <row r="77" spans="1:22">
       <c r="A77" s="31"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="17"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="18"/>
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
       <c r="G77" s="17"/>
@@ -2712,12 +2778,13 @@
       <c r="S77" s="17"/>
       <c r="T77" s="17"/>
       <c r="U77" s="17"/>
-    </row>
-    <row r="78" spans="1:21">
+      <c r="V77" s="17"/>
+    </row>
+    <row r="78" spans="1:22">
       <c r="A78" s="31"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="17"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="18"/>
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
       <c r="G78" s="17"/>
@@ -2735,12 +2802,13 @@
       <c r="S78" s="17"/>
       <c r="T78" s="17"/>
       <c r="U78" s="17"/>
-    </row>
-    <row r="79" spans="1:21">
+      <c r="V78" s="17"/>
+    </row>
+    <row r="79" spans="1:22">
       <c r="A79" s="31"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="17"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="18"/>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
       <c r="G79" s="17"/>
@@ -2758,12 +2826,13 @@
       <c r="S79" s="17"/>
       <c r="T79" s="17"/>
       <c r="U79" s="17"/>
-    </row>
-    <row r="80" spans="1:21">
+      <c r="V79" s="17"/>
+    </row>
+    <row r="80" spans="1:22">
       <c r="A80" s="31"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="17"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="17"/>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
@@ -2781,12 +2850,13 @@
       <c r="S80" s="17"/>
       <c r="T80" s="17"/>
       <c r="U80" s="17"/>
-    </row>
-    <row r="81" spans="1:21">
+      <c r="V80" s="17"/>
+    </row>
+    <row r="81" spans="1:22">
       <c r="A81" s="31"/>
-      <c r="B81" s="32"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="17"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="18"/>
       <c r="E81" s="17"/>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
@@ -2804,12 +2874,13 @@
       <c r="S81" s="17"/>
       <c r="T81" s="17"/>
       <c r="U81" s="17"/>
-    </row>
-    <row r="82" spans="1:21">
+      <c r="V81" s="17"/>
+    </row>
+    <row r="82" spans="1:22">
       <c r="A82" s="31"/>
-      <c r="B82" s="32"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="17"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="18"/>
       <c r="E82" s="17"/>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
@@ -2827,12 +2898,13 @@
       <c r="S82" s="17"/>
       <c r="T82" s="17"/>
       <c r="U82" s="17"/>
-    </row>
-    <row r="83" spans="1:21">
+      <c r="V82" s="17"/>
+    </row>
+    <row r="83" spans="1:22">
       <c r="A83" s="31"/>
-      <c r="B83" s="32"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="17"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="18"/>
       <c r="E83" s="17"/>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
@@ -2850,12 +2922,13 @@
       <c r="S83" s="17"/>
       <c r="T83" s="17"/>
       <c r="U83" s="17"/>
-    </row>
-    <row r="84" spans="1:21">
+      <c r="V83" s="17"/>
+    </row>
+    <row r="84" spans="1:22">
       <c r="A84" s="31"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="17"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="18"/>
       <c r="E84" s="17"/>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
@@ -2873,12 +2946,13 @@
       <c r="S84" s="17"/>
       <c r="T84" s="17"/>
       <c r="U84" s="17"/>
-    </row>
-    <row r="85" spans="1:21">
+      <c r="V84" s="17"/>
+    </row>
+    <row r="85" spans="1:22">
       <c r="A85" s="31"/>
-      <c r="B85" s="32"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="15"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
       <c r="G85" s="15"/>
@@ -2896,12 +2970,13 @@
       <c r="S85" s="15"/>
       <c r="T85" s="15"/>
       <c r="U85" s="15"/>
-    </row>
-    <row r="86" spans="1:21">
+      <c r="V85" s="15"/>
+    </row>
+    <row r="86" spans="1:22">
       <c r="A86" s="33"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="26"/>
+      <c r="B86" s="33"/>
+      <c r="C86" s="34"/>
+      <c r="D86" s="25"/>
       <c r="E86" s="26"/>
       <c r="F86" s="26"/>
       <c r="G86" s="26"/>
@@ -2919,148 +2994,131 @@
       <c r="S86" s="26"/>
       <c r="T86" s="26"/>
       <c r="U86" s="26"/>
-    </row>
-    <row r="87" spans="1:21">
-      <c r="A87" s="50"/>
-      <c r="B87" s="50"/>
-      <c r="C87" s="50"/>
-      <c r="D87" s="50"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="51"/>
-      <c r="K87" s="51"/>
-      <c r="L87" s="51"/>
-      <c r="M87" s="51"/>
-      <c r="N87" s="51"/>
-      <c r="O87" s="51"/>
-      <c r="P87" s="51"/>
-      <c r="Q87" s="51"/>
-      <c r="R87" s="51"/>
-      <c r="S87" s="51"/>
-      <c r="T87" s="51"/>
-      <c r="U87" s="51"/>
-    </row>
-    <row r="88" spans="1:21">
+      <c r="V86" s="26"/>
+    </row>
+    <row r="88" spans="1:22">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
-      <c r="I88" s="36" t="s">
+      <c r="D88" s="10"/>
+      <c r="J88" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="J88" s="36"/>
-      <c r="K88" s="36"/>
-      <c r="L88" s="36"/>
-      <c r="M88" s="36"/>
-      <c r="N88" s="36"/>
-      <c r="O88" s="36"/>
-      <c r="P88" s="36"/>
-      <c r="Q88" s="36"/>
-      <c r="R88" s="36"/>
-      <c r="S88" s="36"/>
-      <c r="T88" s="36"/>
-      <c r="U88" s="36"/>
-    </row>
-    <row r="89" spans="1:21" ht="21" customHeight="1">
+      <c r="K88" s="48"/>
+      <c r="L88" s="48"/>
+      <c r="M88" s="48"/>
+      <c r="N88" s="48"/>
+      <c r="O88" s="48"/>
+      <c r="P88" s="48"/>
+      <c r="Q88" s="48"/>
+      <c r="R88" s="48"/>
+      <c r="S88" s="48"/>
+      <c r="T88" s="48"/>
+      <c r="U88" s="48"/>
+      <c r="V88" s="48"/>
+    </row>
+    <row r="89" spans="1:22" ht="21" customHeight="1">
       <c r="A89" s="11"/>
-      <c r="B89" s="37" t="s">
+      <c r="B89" s="11"/>
+      <c r="C89" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="37"/>
-      <c r="H89" s="37" t="s">
+      <c r="D89" s="49"/>
+      <c r="I89" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="I89" s="37"/>
-      <c r="J89" s="37"/>
-      <c r="K89" s="37"/>
-      <c r="L89" s="37"/>
-      <c r="M89" s="37"/>
-      <c r="N89" s="37"/>
-      <c r="O89" s="37"/>
-      <c r="P89" s="37"/>
-      <c r="Q89" s="37"/>
-      <c r="R89" s="37"/>
-      <c r="S89" s="37"/>
-      <c r="T89" s="37"/>
-      <c r="U89" s="37"/>
-    </row>
-    <row r="90" spans="1:21">
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
+      <c r="L89" s="49"/>
+      <c r="M89" s="49"/>
+      <c r="N89" s="49"/>
+      <c r="O89" s="49"/>
+      <c r="P89" s="49"/>
+      <c r="Q89" s="49"/>
+      <c r="R89" s="49"/>
+      <c r="S89" s="49"/>
+      <c r="T89" s="49"/>
+      <c r="U89" s="49"/>
+      <c r="V89" s="49"/>
+    </row>
+    <row r="90" spans="1:22">
       <c r="A90" s="12"/>
-      <c r="B90" s="36" t="s">
+      <c r="B90" s="12"/>
+      <c r="C90" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="36"/>
-      <c r="H90" s="36" t="s">
+      <c r="D90" s="48"/>
+      <c r="I90" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="I90" s="36"/>
-      <c r="J90" s="36"/>
-      <c r="K90" s="36"/>
-      <c r="L90" s="36"/>
-      <c r="M90" s="36"/>
-      <c r="N90" s="36"/>
-      <c r="O90" s="36"/>
-      <c r="P90" s="36"/>
-      <c r="Q90" s="36"/>
-      <c r="R90" s="36"/>
-      <c r="S90" s="36"/>
-      <c r="T90" s="36"/>
-      <c r="U90" s="36"/>
-    </row>
-    <row r="91" spans="1:21" ht="18" customHeight="1">
+      <c r="J90" s="48"/>
+      <c r="K90" s="48"/>
+      <c r="L90" s="48"/>
+      <c r="M90" s="48"/>
+      <c r="N90" s="48"/>
+      <c r="O90" s="48"/>
+      <c r="P90" s="48"/>
+      <c r="Q90" s="48"/>
+      <c r="R90" s="48"/>
+      <c r="S90" s="48"/>
+      <c r="T90" s="48"/>
+      <c r="U90" s="48"/>
+      <c r="V90" s="48"/>
+    </row>
+    <row r="91" spans="1:22" ht="18" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="J88:V88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="I89:V89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="I90:V90"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:R10"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="K6:V6"/>
+    <mergeCell ref="J2:V2"/>
+    <mergeCell ref="J3:V3"/>
     <mergeCell ref="A7:A10"/>
-    <mergeCell ref="B7:B10"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="D7:D10"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="J1:U1"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="I2:U2"/>
-    <mergeCell ref="I3:U3"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:U7"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="I88:U88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="H89:U89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="H90:U90"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="B7:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="33" orientation="portrait" r:id="rId1"/>
